--- a/2026/DRAGO/Abril/EXPENSAS-Abril.xlsx
+++ b/2026/DRAGO/Abril/EXPENSAS-Abril.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\DRAGO\Abril\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\DRAGO\Abril\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB430C10-3475-46B9-9071-869D248EF125}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9908116C-CF53-4A8C-873C-EF88E30AA5FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="detalle y gastos" sheetId="3" r:id="rId1"/>
@@ -18,15 +18,20 @@
     <sheet name="extraordinarias" sheetId="4" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'detalle y gastos'!$A$1:$C$50</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'detalle y gastos'!$A$1:$C$48</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'prorrateo '!$A$1:$M$32</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="91">
   <si>
     <t>UF</t>
   </si>
@@ -184,9 +189,6 @@
     <t>Pago</t>
   </si>
   <si>
-    <t>DEUDA</t>
-  </si>
-  <si>
     <t>TOTAL A PAGAR</t>
   </si>
   <si>
@@ -283,18 +285,6 @@
     <t xml:space="preserve">Sueldo Sra. Gisela </t>
   </si>
   <si>
-    <t>Seguro Sra. Gisela - Provisiorio</t>
-  </si>
-  <si>
-    <t>AUMENTADOS EN 3n3r0 2026</t>
-  </si>
-  <si>
-    <t>Fumigacion - Sr. Nicolas</t>
-  </si>
-  <si>
-    <t>No llego Fac.</t>
-  </si>
-  <si>
     <t>Vto. 15/05</t>
   </si>
   <si>
@@ -302,6 +292,18 @@
   </si>
   <si>
     <t>Período ABRIL 2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seguro Sra. Gisela </t>
+  </si>
+  <si>
+    <t>AUMENTADOS EN 4BR1L 2026</t>
+  </si>
+  <si>
+    <t>Fumigacion - Sr. Nicolas - Mes anterior - Se adeuda este mes por falta de comprobante</t>
+  </si>
+  <si>
+    <t>Deuda o saldo a favor</t>
   </si>
 </sst>
 </file>
@@ -841,7 +843,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="130">
+  <cellXfs count="128">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1005,12 +1007,30 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="11" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="11" fillId="6" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -1032,21 +1052,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="25" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1062,13 +1067,8 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="6" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="16" fillId="6" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="11" fillId="6" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1148,9 +1148,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1188,9 +1188,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1223,9 +1223,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1258,9 +1275,26 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1437,61 +1471,61 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:H59"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A2:H57"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
-    <col min="2" max="2" width="40.33203125" customWidth="1"/>
-    <col min="3" max="3" width="16.44140625" customWidth="1"/>
-    <col min="4" max="4" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="40.28515625" customWidth="1"/>
+    <col min="3" max="3" width="16.42578125" customWidth="1"/>
+    <col min="4" max="4" width="12.140625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>17</v>
       </c>
       <c r="C2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B4" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3"/>
       <c r="B5" s="21"/>
       <c r="C5" s="3"/>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="22" t="s">
         <v>35</v>
       </c>
       <c r="B7" s="23" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="C7" s="23" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="3"/>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>37</v>
       </c>
@@ -1499,7 +1533,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>38</v>
       </c>
@@ -1507,387 +1541,364 @@
         <v>46</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="19" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="53" t="s">
         <v>12</v>
       </c>
       <c r="B16" s="46"/>
-      <c r="C16" s="129"/>
-    </row>
-    <row r="17" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C16" s="107"/>
+    </row>
+    <row r="17" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="46" t="s">
         <v>49</v>
       </c>
       <c r="B17" s="54" t="s">
-        <v>71</v>
-      </c>
-      <c r="C17" s="126">
+        <v>70</v>
+      </c>
+      <c r="C17" s="106">
         <v>48091.199999999997</v>
       </c>
       <c r="D17" s="5"/>
       <c r="E17" s="12"/>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="46" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B18" s="55"/>
-      <c r="C18" s="126">
+      <c r="C18" s="106">
         <v>5842.51</v>
       </c>
       <c r="D18" s="38"/>
       <c r="E18" s="12"/>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="46" t="s">
         <v>42</v>
       </c>
       <c r="B19" s="56" t="s">
-        <v>63</v>
-      </c>
-      <c r="C19" s="126">
-        <v>21586.43</v>
+        <v>62</v>
+      </c>
+      <c r="C19" s="106">
+        <v>21662.29</v>
       </c>
       <c r="D19" s="5"/>
       <c r="E19" s="12"/>
       <c r="F19" s="14"/>
       <c r="H19" s="86"/>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="46" t="s">
         <v>31</v>
       </c>
       <c r="B20" s="56"/>
-      <c r="C20" s="128">
-        <v>200669.44</v>
+      <c r="C20" s="127">
+        <v>204993.04</v>
       </c>
       <c r="D20" s="38"/>
       <c r="F20" s="12"/>
       <c r="H20" s="86"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="46" t="s">
-        <v>31</v>
-      </c>
-      <c r="B21" s="56"/>
-      <c r="C21" s="128">
-        <v>592940.62</v>
-      </c>
-      <c r="D21" s="38"/>
-      <c r="F21" s="12"/>
-      <c r="H21" s="86"/>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A22" s="46" t="s">
         <v>32</v>
       </c>
-      <c r="B22" s="56" t="s">
-        <v>62</v>
-      </c>
-      <c r="C22" s="106">
-        <v>57191</v>
-      </c>
-      <c r="D22" s="5"/>
-      <c r="E22" s="12"/>
-      <c r="H22" t="s">
+      <c r="B21" s="56" t="s">
+        <v>61</v>
+      </c>
+      <c r="C21" s="106">
+        <v>60500</v>
+      </c>
+      <c r="D21" s="5"/>
+      <c r="E21" s="12"/>
+      <c r="H21" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" s="57"/>
+      <c r="B22" s="58"/>
+      <c r="C22" s="42">
+        <f>SUM(C17:C21)</f>
+        <v>341089.04000000004</v>
+      </c>
+      <c r="E22" s="86"/>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" s="53" t="s">
+        <v>33</v>
+      </c>
+      <c r="B23" s="56"/>
+      <c r="C23" s="84"/>
+    </row>
+    <row r="24" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A24" s="46" t="s">
+        <v>83</v>
+      </c>
+      <c r="B24" s="59" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A23" s="57"/>
-      <c r="B23" s="58"/>
-      <c r="C23" s="42">
-        <f>SUM(C17:C22)</f>
-        <v>926321.2</v>
-      </c>
-      <c r="E23" s="86"/>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A24" s="53" t="s">
-        <v>33</v>
-      </c>
-      <c r="B24" s="56"/>
-      <c r="C24" s="84"/>
-    </row>
-    <row r="25" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="C24" s="106">
+        <v>64694.7</v>
+      </c>
+      <c r="F24" s="18"/>
+    </row>
+    <row r="25" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" s="46" t="s">
-        <v>84</v>
-      </c>
-      <c r="B25" s="59" t="s">
-        <v>91</v>
-      </c>
+        <v>89</v>
+      </c>
+      <c r="B25" s="59"/>
       <c r="C25" s="106">
-        <f>71883+71883*20%</f>
-        <v>86259.6</v>
+        <v>50000</v>
       </c>
       <c r="F25" s="18"/>
     </row>
-    <row r="26" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" s="46" t="s">
-        <v>87</v>
-      </c>
-      <c r="B26" s="59" t="s">
-        <v>88</v>
-      </c>
+        <v>82</v>
+      </c>
+      <c r="B26" s="59"/>
       <c r="C26" s="106">
-        <v>0</v>
+        <v>80000</v>
       </c>
       <c r="F26" s="18"/>
     </row>
-    <row r="27" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" s="46" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B27" s="59"/>
       <c r="C27" s="106">
-        <v>80000</v>
+        <v>0</v>
       </c>
       <c r="F27" s="18"/>
     </row>
-    <row r="28" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A28" s="127"/>
-      <c r="B28" s="59"/>
-      <c r="C28" s="126">
-        <v>10000</v>
-      </c>
+    <row r="28" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A28" s="46" t="s">
+        <v>65</v>
+      </c>
+      <c r="B28" s="56"/>
+      <c r="C28" s="52"/>
+      <c r="D28" s="5"/>
+      <c r="E28" s="12"/>
       <c r="F28" s="18"/>
     </row>
-    <row r="29" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A29" s="46" t="s">
-        <v>81</v>
-      </c>
-      <c r="B29" s="59"/>
-      <c r="C29" s="106">
-        <v>0</v>
+    <row r="29" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A29" s="57"/>
+      <c r="B29" s="58"/>
+      <c r="C29" s="42">
+        <f>SUM(C23:C28)</f>
+        <v>194694.7</v>
       </c>
       <c r="F29" s="18"/>
     </row>
-    <row r="30" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A30" s="46" t="s">
-        <v>66</v>
-      </c>
-      <c r="B30" s="56"/>
-      <c r="C30" s="52"/>
-      <c r="D30" s="5"/>
-      <c r="E30" s="12"/>
+    <row r="30" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A30" s="49" t="s">
+        <v>64</v>
+      </c>
+      <c r="B30" s="49"/>
+      <c r="C30" s="60">
+        <f>+C29+C22</f>
+        <v>535783.74</v>
+      </c>
       <c r="F30" s="18"/>
     </row>
-    <row r="31" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A31" s="57"/>
-      <c r="B31" s="58"/>
-      <c r="C31" s="42">
-        <f>SUM(C24:C30)</f>
-        <v>176259.6</v>
-      </c>
+    <row r="31" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="C31" s="43"/>
       <c r="F31" s="18"/>
     </row>
-    <row r="32" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A32" s="49" t="s">
-        <v>65</v>
-      </c>
-      <c r="B32" s="49"/>
-      <c r="C32" s="60">
-        <f>+C31+C23</f>
-        <v>1102580.8</v>
-      </c>
+    <row r="32" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A32" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="C32" s="43"/>
       <c r="F32" s="18"/>
     </row>
-    <row r="33" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="C33" s="43"/>
+    <row r="33" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A33" s="108"/>
+      <c r="B33" s="109"/>
+      <c r="C33" s="100"/>
       <c r="F33" s="18"/>
     </row>
-    <row r="34" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A34" s="19" t="s">
-        <v>43</v>
-      </c>
-      <c r="C34" s="43"/>
+    <row r="34" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A34" s="104"/>
+      <c r="B34" s="46"/>
+      <c r="C34" s="51"/>
       <c r="F34" s="18"/>
     </row>
-    <row r="35" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A35" s="107"/>
-      <c r="B35" s="108"/>
-      <c r="C35" s="100"/>
+    <row r="35" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A35" s="46"/>
+      <c r="B35" s="46"/>
+      <c r="C35" s="52"/>
       <c r="F35" s="18"/>
     </row>
-    <row r="36" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A36" s="104"/>
-      <c r="B36" s="46"/>
-      <c r="C36" s="51"/>
+    <row r="36" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="C36" s="44"/>
       <c r="F36" s="18"/>
     </row>
-    <row r="37" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A37" s="46"/>
-      <c r="B37" s="46"/>
-      <c r="C37" s="52"/>
-      <c r="F37" s="18"/>
-    </row>
-    <row r="38" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="C38" s="44"/>
-      <c r="F38" s="18"/>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A39" s="19" t="s">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="B39" s="19"/>
-      <c r="C39" s="20">
-        <f>SUM(C35:C38)</f>
-        <v>0</v>
-      </c>
-      <c r="E39" s="12"/>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A41" s="29" t="s">
+      <c r="B37" s="19"/>
+      <c r="C37" s="20">
+        <f>SUM(C33:C36)</f>
+        <v>0</v>
+      </c>
+      <c r="E37" s="12"/>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="B41" s="29"/>
-      <c r="C41" s="30">
-        <f>+C39+C32</f>
-        <v>1102580.8</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A43" s="5" t="s">
+      <c r="B39" s="29"/>
+      <c r="C39" s="30">
+        <f>+C37+C30</f>
+        <v>535783.74</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="5" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A44" s="31" t="s">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="B44" s="28"/>
-      <c r="C44" s="33">
-        <v>-244667.59247391066</v>
-      </c>
-      <c r="D44" s="6"/>
-      <c r="E44" s="6"/>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B42" s="28"/>
+      <c r="C42" s="33">
+        <v>-272851.17727391061</v>
+      </c>
+      <c r="D42" s="6"/>
+      <c r="E42" s="6"/>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>8</v>
+      </c>
+      <c r="C43" s="27">
+        <f>'prorrateo '!F13</f>
+        <v>608844.89348399988</v>
+      </c>
+      <c r="D43" s="12"/>
+      <c r="E43" s="12"/>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>79</v>
+      </c>
+      <c r="C44" s="105">
+        <f>extraordinarias!E13</f>
+        <v>0</v>
+      </c>
+      <c r="D44" s="12"/>
+      <c r="E44" s="12"/>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>8</v>
-      </c>
-      <c r="C45" s="27">
-        <f>'prorrateo '!F13</f>
-        <v>473591.13520000002</v>
+        <v>72</v>
+      </c>
+      <c r="C45" s="105">
+        <f>-C37</f>
+        <v>0</v>
       </c>
       <c r="D45" s="12"/>
       <c r="E45" s="12"/>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>80</v>
-      </c>
-      <c r="C46" s="105">
-        <f>extraordinarias!E13</f>
-        <v>0</v>
-      </c>
-      <c r="D46" s="12"/>
-      <c r="E46" s="12"/>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A47" t="s">
-        <v>73</v>
-      </c>
-      <c r="C47" s="105">
-        <f>-C39</f>
-        <v>0</v>
-      </c>
-      <c r="D47" s="12"/>
-      <c r="E47" s="12"/>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A48" t="s">
-        <v>64</v>
-      </c>
-      <c r="C48" s="61">
-        <f>-(C32-C30)</f>
-        <v>-1102580.8</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A49" s="31" t="s">
+        <v>63</v>
+      </c>
+      <c r="C46" s="61">
+        <f>-(C30-C28)</f>
+        <v>-535783.74</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" s="31" t="s">
         <v>15</v>
       </c>
-      <c r="B49" s="28"/>
-      <c r="C49" s="33">
-        <f>SUM(C44:C48)</f>
-        <v>-873657.25727391068</v>
-      </c>
-      <c r="D49" s="6"/>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B47" s="28"/>
+      <c r="C47" s="33">
+        <f>SUM(C42:C46)</f>
+        <v>-199790.02378991072</v>
+      </c>
+      <c r="D47" s="6"/>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48" s="15"/>
+      <c r="B48" s="14"/>
+      <c r="C48" s="16"/>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" s="15"/>
+      <c r="B49" s="14"/>
+      <c r="C49" s="16"/>
+      <c r="F49" s="62"/>
+    </row>
+    <row r="50" spans="1:6" ht="2.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="15"/>
       <c r="B50" s="14"/>
       <c r="C50" s="16"/>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A51" s="15"/>
-      <c r="B51" s="14"/>
-      <c r="C51" s="16"/>
-      <c r="F51" s="62"/>
-    </row>
-    <row r="52" spans="1:6" ht="2.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="15"/>
-      <c r="B52" s="14"/>
-      <c r="C52" s="16"/>
-    </row>
-    <row r="53" spans="1:6" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="45" t="s">
-        <v>60</v>
-      </c>
-      <c r="B53" s="64"/>
-      <c r="C53" s="65">
+    <row r="51" spans="1:6" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="45" t="s">
+        <v>59</v>
+      </c>
+      <c r="B51" s="64"/>
+      <c r="C51" s="65">
         <v>109834.99657000002</v>
       </c>
     </row>
-    <row r="54" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="46"/>
-      <c r="B54" s="46"/>
-      <c r="C54" s="50"/>
-    </row>
-    <row r="55" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="49" t="s">
+    <row r="52" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="46"/>
+      <c r="B52" s="46"/>
+      <c r="C52" s="50"/>
+    </row>
+    <row r="53" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="49" t="s">
         <v>4</v>
       </c>
-      <c r="B55" s="47"/>
-      <c r="C55" s="48">
-        <f>SUM(C53:C54)</f>
+      <c r="B53" s="47"/>
+      <c r="C53" s="48">
+        <f>SUM(C51:C52)</f>
         <v>109834.99657000002</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54" s="14"/>
+      <c r="B54" s="14"/>
+      <c r="C54" s="14"/>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A55" s="14"/>
+      <c r="B55" s="14"/>
+      <c r="C55" s="14"/>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="14"/>
       <c r="B56" s="14"/>
       <c r="C56" s="14"/>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="14"/>
       <c r="B57" s="14"/>
       <c r="C57" s="14"/>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A58" s="14"/>
-      <c r="B58" s="14"/>
-      <c r="C58" s="14"/>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A59" s="14"/>
-      <c r="B59" s="14"/>
-      <c r="C59" s="14"/>
-    </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="A33:B33"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="B4" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
@@ -1905,36 +1916,36 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:Q39"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.33203125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="5.28515625" style="1" customWidth="1"/>
     <col min="2" max="2" width="8" style="1" customWidth="1"/>
-    <col min="3" max="3" width="23.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.33203125" customWidth="1"/>
-    <col min="6" max="6" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.44140625" customWidth="1"/>
-    <col min="8" max="8" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.44140625" customWidth="1"/>
-    <col min="10" max="10" width="9.109375" customWidth="1"/>
-    <col min="11" max="12" width="12.44140625" customWidth="1"/>
-    <col min="13" max="13" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="11.44140625" style="17"/>
+    <col min="3" max="3" width="23.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.28515625" customWidth="1"/>
+    <col min="6" max="6" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.42578125" customWidth="1"/>
+    <col min="8" max="8" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.42578125" customWidth="1"/>
+    <col min="10" max="10" width="9.140625" customWidth="1"/>
+    <col min="11" max="12" width="12.42578125" customWidth="1"/>
+    <col min="13" max="13" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.42578125" style="17"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="40" t="s">
         <v>47</v>
       </c>
       <c r="E1" s="102">
-        <v>501774.72</v>
+        <v>535783.74</v>
       </c>
       <c r="G1" t="str">
         <f>'detalle y gastos'!C7</f>
         <v>Vto. 15/05</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" s="71" t="str">
         <f>'detalle y gastos'!B7</f>
         <v>LIQUIDACIÓN EXPENSAS ABRIL 2025</v>
@@ -1954,61 +1965,61 @@
       <c r="L2" s="66"/>
       <c r="M2" s="67"/>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A3" s="119"/>
-      <c r="B3" s="116" t="s">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A3" s="113"/>
+      <c r="B3" s="111" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="113" t="s">
+      <c r="C3" s="119" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="114" t="s">
-        <v>54</v>
-      </c>
-      <c r="E3" s="116" t="s">
+      <c r="D3" s="120" t="s">
+        <v>53</v>
+      </c>
+      <c r="E3" s="111" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="111" t="s">
+      <c r="F3" s="117" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="113" t="s">
-        <v>52</v>
-      </c>
-      <c r="H3" s="111" t="s">
+      <c r="G3" s="120" t="s">
+        <v>90</v>
+      </c>
+      <c r="H3" s="117" t="s">
         <v>44</v>
       </c>
-      <c r="I3" s="113" t="s">
+      <c r="I3" s="119" t="s">
         <v>6</v>
       </c>
-      <c r="J3" s="115" t="s">
-        <v>77</v>
-      </c>
-      <c r="K3" s="109" t="s">
+      <c r="J3" s="121" t="s">
+        <v>76</v>
+      </c>
+      <c r="K3" s="115" t="s">
+        <v>66</v>
+      </c>
+      <c r="L3" s="115" t="s">
         <v>67</v>
       </c>
-      <c r="L3" s="109" t="s">
+      <c r="M3" s="115" t="s">
         <v>68</v>
       </c>
-      <c r="M3" s="109" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A4" s="120"/>
-      <c r="B4" s="117"/>
-      <c r="C4" s="113"/>
-      <c r="D4" s="114"/>
-      <c r="E4" s="117"/>
-      <c r="F4" s="112"/>
-      <c r="G4" s="113"/>
-      <c r="H4" s="112"/>
-      <c r="I4" s="113"/>
-      <c r="J4" s="115"/>
-      <c r="K4" s="110"/>
-      <c r="L4" s="110"/>
-      <c r="M4" s="110"/>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A4" s="114"/>
+      <c r="B4" s="112"/>
+      <c r="C4" s="119"/>
+      <c r="D4" s="120"/>
+      <c r="E4" s="112"/>
+      <c r="F4" s="118"/>
+      <c r="G4" s="120"/>
+      <c r="H4" s="118"/>
+      <c r="I4" s="119"/>
+      <c r="J4" s="121"/>
+      <c r="K4" s="116"/>
+      <c r="L4" s="116"/>
+      <c r="M4" s="116"/>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" s="68">
         <v>1</v>
       </c>
@@ -2019,17 +2030,17 @@
         <v>26</v>
       </c>
       <c r="D5" s="41" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E5" s="37">
-        <v>65797.136979999981</v>
+        <v>60506.878099999973</v>
       </c>
       <c r="F5" s="85">
-        <v>66005</v>
+        <v>60715</v>
       </c>
       <c r="G5" s="37">
         <f>E5-F5</f>
-        <v>-207.86302000001888</v>
+        <v>-208.12190000002738</v>
       </c>
       <c r="H5" s="37">
         <f>IF(G5&gt;0,G5*3%,0)</f>
@@ -2041,18 +2052,18 @@
       <c r="J5" s="63"/>
       <c r="K5" s="75">
         <f>E1*I5</f>
-        <v>60714.741119999991</v>
+        <v>64829.832539999996</v>
       </c>
       <c r="L5" s="75">
         <f>E5-F5+H5+K5+J5</f>
-        <v>60506.878099999973</v>
+        <v>64621.710639999968</v>
       </c>
       <c r="M5" s="76">
         <f>L5+L5*4%</f>
-        <v>62927.153223999972</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
+        <v>67206.579065599974</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" s="68">
         <v>2</v>
       </c>
@@ -2063,14 +2074,14 @@
         <v>27</v>
       </c>
       <c r="D6" s="41" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E6" s="37">
-        <v>66549.584799999982</v>
+        <v>61216.515839999993</v>
       </c>
       <c r="F6" s="85">
         <f>E6</f>
-        <v>66549.584799999982</v>
+        <v>61216.515839999993</v>
       </c>
       <c r="G6" s="37">
         <f t="shared" ref="G6:G12" si="0">E6-F6</f>
@@ -2086,20 +2097,20 @@
       <c r="J6" s="63"/>
       <c r="K6" s="75">
         <f>E1*I6</f>
-        <v>61216.515839999993</v>
+        <v>65365.616279999995</v>
       </c>
       <c r="L6" s="75">
         <f t="shared" ref="L6:L12" si="2">E6-F6+H6+K6+J6</f>
-        <v>61216.515839999993</v>
+        <v>65365.616279999995</v>
       </c>
       <c r="M6" s="76">
         <f t="shared" ref="M6:M12" si="3">L6+L6*4%</f>
-        <v>63665.17647359999</v>
+        <v>67980.240931199995</v>
       </c>
       <c r="O6" s="83"/>
       <c r="Q6" s="82"/>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" s="68">
         <v>3</v>
       </c>
@@ -2110,14 +2121,14 @@
         <v>28</v>
       </c>
       <c r="D7" s="41" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E7" s="37">
-        <v>63822.142799999994</v>
+        <v>58707.642240000001</v>
       </c>
       <c r="F7" s="85">
         <f>E7</f>
-        <v>63822.142799999994</v>
+        <v>58707.642240000001</v>
       </c>
       <c r="G7" s="37">
         <f t="shared" si="0"/>
@@ -2133,18 +2144,18 @@
       <c r="J7" s="63"/>
       <c r="K7" s="75">
         <f>E1*I7</f>
-        <v>58707.642240000001</v>
+        <v>62686.69758</v>
       </c>
       <c r="L7" s="75">
         <f t="shared" si="2"/>
-        <v>58707.642240000001</v>
+        <v>62686.69758</v>
       </c>
       <c r="M7" s="76">
         <f t="shared" si="3"/>
-        <v>61055.947929599999</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
+        <v>65194.165483199999</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" s="68">
         <v>4</v>
       </c>
@@ -2155,21 +2166,22 @@
         <v>29</v>
       </c>
       <c r="D8" s="41" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E8" s="85">
-        <v>63822.142799999994</v>
+        <v>61407.419323999995</v>
       </c>
       <c r="F8" s="85">
-        <v>61201</v>
+        <f>E8</f>
+        <v>61407.419323999995</v>
       </c>
       <c r="G8" s="37">
         <f t="shared" si="0"/>
-        <v>2621.1427999999942</v>
+        <v>0</v>
       </c>
       <c r="H8" s="37">
         <f t="shared" si="1"/>
-        <v>78.634283999999823</v>
+        <v>0</v>
       </c>
       <c r="I8" s="74">
         <v>0.11700000000000001</v>
@@ -2177,21 +2189,21 @@
       <c r="J8" s="63"/>
       <c r="K8" s="75">
         <f>E1*I8</f>
-        <v>58707.642240000001</v>
+        <v>62686.69758</v>
       </c>
       <c r="L8" s="75">
         <f t="shared" si="2"/>
-        <v>61407.419323999995</v>
+        <v>62686.69758</v>
       </c>
       <c r="M8" s="76">
         <f t="shared" si="3"/>
-        <v>63863.716096959994</v>
+        <v>65194.165483199999</v>
       </c>
       <c r="N8" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="68">
         <v>5</v>
       </c>
@@ -2202,14 +2214,14 @@
         <v>26</v>
       </c>
       <c r="D9" s="41" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E9" s="37">
-        <v>74731.910799999998</v>
+        <v>68743.136639999997</v>
       </c>
       <c r="F9" s="85">
         <f>E9</f>
-        <v>74731.910799999998</v>
+        <v>68743.136639999997</v>
       </c>
       <c r="G9" s="37">
         <f t="shared" si="0"/>
@@ -2225,18 +2237,18 @@
       <c r="J9" s="63"/>
       <c r="K9" s="75">
         <f>E1*I9</f>
-        <v>68743.136639999997</v>
+        <v>73402.372380000001</v>
       </c>
       <c r="L9" s="75">
         <f t="shared" si="2"/>
-        <v>68743.136639999997</v>
+        <v>73402.372380000001</v>
       </c>
       <c r="M9" s="76">
         <f t="shared" si="3"/>
-        <v>71492.862105599997</v>
-      </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
+        <v>76338.467275200004</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" s="68">
         <v>6</v>
       </c>
@@ -2247,21 +2259,21 @@
         <v>26</v>
       </c>
       <c r="D10" s="41" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E10" s="37">
-        <v>226453.92768934212</v>
+        <v>225317.20446002239</v>
       </c>
       <c r="F10" s="85">
-        <v>72004.47</v>
+        <v>234329.79</v>
       </c>
       <c r="G10" s="37">
         <f t="shared" si="0"/>
-        <v>154449.45768934212</v>
+        <v>-9012.5855399776192</v>
       </c>
       <c r="H10" s="37">
         <f t="shared" si="1"/>
-        <v>4633.4837306802638</v>
+        <v>0</v>
       </c>
       <c r="I10" s="74">
         <v>0.13200000000000001</v>
@@ -2269,18 +2281,18 @@
       <c r="J10" s="63"/>
       <c r="K10" s="75">
         <f>E1*I10</f>
-        <v>66234.263040000005</v>
+        <v>70723.453680000006</v>
       </c>
       <c r="L10" s="75">
         <f t="shared" si="2"/>
-        <v>225317.20446002239</v>
+        <v>61710.868140022387</v>
       </c>
       <c r="M10" s="76">
         <f t="shared" si="3"/>
-        <v>234329.89263842328</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
+        <v>64179.302865623285</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" s="68">
         <v>7</v>
       </c>
@@ -2291,19 +2303,19 @@
         <v>28</v>
       </c>
       <c r="D11" s="41" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E11" s="37">
-        <v>69277.026799999992</v>
+        <v>135080.727044</v>
       </c>
       <c r="F11" s="85"/>
       <c r="G11" s="37">
         <f t="shared" si="0"/>
-        <v>69277.026799999992</v>
+        <v>135080.727044</v>
       </c>
       <c r="H11" s="37">
         <f t="shared" si="1"/>
-        <v>2078.3108039999997</v>
+        <v>4052.42181132</v>
       </c>
       <c r="I11" s="74">
         <v>0.127</v>
@@ -2311,18 +2323,18 @@
       <c r="J11" s="63"/>
       <c r="K11" s="75">
         <f>E1*I11</f>
-        <v>63725.389439999999</v>
+        <v>68044.534979999997</v>
       </c>
       <c r="L11" s="75">
         <f t="shared" si="2"/>
-        <v>135080.727044</v>
+        <v>207177.68383532</v>
       </c>
       <c r="M11" s="76">
         <f t="shared" si="3"/>
-        <v>140483.95612575999</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
+        <v>215464.79118873281</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" s="68">
         <v>8</v>
       </c>
@@ -2333,14 +2345,14 @@
         <v>30</v>
       </c>
       <c r="D12" s="41" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E12" s="37">
-        <v>69277.026799999992</v>
+        <v>63725.389439999999</v>
       </c>
       <c r="F12" s="85">
         <f>E12</f>
-        <v>69277.026799999992</v>
+        <v>63725.389439999999</v>
       </c>
       <c r="G12" s="37">
         <f t="shared" si="0"/>
@@ -2356,18 +2368,18 @@
       <c r="J12" s="63"/>
       <c r="K12" s="75">
         <f>E1*I12</f>
-        <v>63725.389439999999</v>
+        <v>68044.534979999997</v>
       </c>
       <c r="L12" s="75">
         <f t="shared" si="2"/>
-        <v>63725.389439999999</v>
+        <v>68044.534979999997</v>
       </c>
       <c r="M12" s="76">
         <f t="shared" si="3"/>
-        <v>66274.405017600002</v>
-      </c>
-    </row>
-    <row r="13" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>70766.316379199998</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="77" t="s">
         <v>10</v>
       </c>
@@ -2376,16 +2388,16 @@
       <c r="D13" s="79"/>
       <c r="E13" s="80">
         <f>SUM(E5:E12)</f>
-        <v>699730.89946934208</v>
+        <v>734704.9130880225</v>
       </c>
       <c r="F13" s="69">
         <f>SUM(F5:F12)</f>
-        <v>473591.13520000002</v>
+        <v>608844.89348399988</v>
       </c>
       <c r="G13" s="69"/>
       <c r="H13" s="69">
         <f>SUM(H5:H12)</f>
-        <v>6790.4288186802632</v>
+        <v>4052.42181132</v>
       </c>
       <c r="I13" s="70">
         <f t="shared" ref="I13" si="4">SUM(I5:I12)</f>
@@ -2397,355 +2409,350 @@
       </c>
       <c r="K13" s="80">
         <f>SUM(K5:K12)</f>
-        <v>501774.72</v>
+        <v>535783.74</v>
       </c>
       <c r="L13" s="80">
         <f>SUM(L5:L12)</f>
-        <v>734704.9130880225</v>
+        <v>665696.18141534238</v>
       </c>
       <c r="M13" s="81">
         <f>SUM(M5:M12)</f>
-        <v>764093.10961154324</v>
-      </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="C15" s="118" t="s">
-        <v>78</v>
-      </c>
-      <c r="D15" s="118"/>
-      <c r="E15" s="118"/>
-      <c r="F15" s="118"/>
-      <c r="G15" s="118"/>
-      <c r="H15" s="118"/>
-      <c r="I15" s="118"/>
-      <c r="J15" s="118"/>
-      <c r="K15" s="118"/>
-      <c r="L15" s="118"/>
-    </row>
-    <row r="16" spans="1:17" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+        <v>692324.02867195604</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="C15" s="110" t="s">
+        <v>77</v>
+      </c>
+      <c r="D15" s="110"/>
+      <c r="E15" s="110"/>
+      <c r="F15" s="110"/>
+      <c r="G15" s="110"/>
+      <c r="H15" s="110"/>
+      <c r="I15" s="110"/>
+      <c r="J15" s="110"/>
+      <c r="K15" s="110"/>
+      <c r="L15" s="110"/>
+    </row>
+    <row r="16" spans="1:17" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="40" t="s">
         <v>48</v>
       </c>
-      <c r="C16" s="118"/>
-      <c r="D16" s="118"/>
-      <c r="E16" s="118"/>
-      <c r="F16" s="118"/>
-      <c r="G16" s="118"/>
-      <c r="H16" s="118"/>
-      <c r="I16" s="118"/>
-      <c r="J16" s="118"/>
-      <c r="K16" s="118"/>
-      <c r="L16" s="118"/>
-    </row>
-    <row r="17" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C16" s="110"/>
+      <c r="D16" s="110"/>
+      <c r="E16" s="110"/>
+      <c r="F16" s="110"/>
+      <c r="G16" s="110"/>
+      <c r="H16" s="110"/>
+      <c r="I16" s="110"/>
+      <c r="J16" s="110"/>
+      <c r="K16" s="110"/>
+      <c r="L16" s="110"/>
+    </row>
+    <row r="17" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="24" t="s">
         <v>50</v>
       </c>
       <c r="B17" s="25"/>
-      <c r="C17" s="118"/>
-      <c r="D17" s="118"/>
-      <c r="E17" s="118"/>
-      <c r="F17" s="118"/>
-      <c r="G17" s="118"/>
-      <c r="H17" s="118"/>
-      <c r="I17" s="118"/>
-      <c r="J17" s="118"/>
-      <c r="K17" s="118"/>
-      <c r="L17" s="118"/>
+      <c r="C17" s="110"/>
+      <c r="D17" s="110"/>
+      <c r="E17" s="110"/>
+      <c r="F17" s="110"/>
+      <c r="G17" s="110"/>
+      <c r="H17" s="110"/>
+      <c r="I17" s="110"/>
+      <c r="J17" s="110"/>
+      <c r="K17" s="110"/>
+      <c r="L17" s="110"/>
       <c r="M17" s="26"/>
     </row>
-    <row r="18" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B18" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C18" s="118"/>
-      <c r="D18" s="118"/>
-      <c r="E18" s="118"/>
-      <c r="F18" s="118"/>
-      <c r="G18" s="118"/>
-      <c r="H18" s="118"/>
-      <c r="I18" s="118"/>
-      <c r="J18" s="118"/>
-      <c r="K18" s="118"/>
-      <c r="L18" s="118"/>
+      <c r="C18" s="110"/>
+      <c r="D18" s="110"/>
+      <c r="E18" s="110"/>
+      <c r="F18" s="110"/>
+      <c r="G18" s="110"/>
+      <c r="H18" s="110"/>
+      <c r="I18" s="110"/>
+      <c r="J18" s="110"/>
+      <c r="K18" s="110"/>
+      <c r="L18" s="110"/>
       <c r="M18" s="36" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2"/>
       <c r="B19" s="7"/>
-      <c r="C19" s="118"/>
-      <c r="D19" s="118"/>
-      <c r="E19" s="118"/>
-      <c r="F19" s="118"/>
-      <c r="G19" s="118"/>
-      <c r="H19" s="118"/>
-      <c r="I19" s="118"/>
-      <c r="J19" s="118"/>
-      <c r="K19" s="118"/>
-      <c r="L19" s="118"/>
+      <c r="C19" s="110"/>
+      <c r="D19" s="110"/>
+      <c r="E19" s="110"/>
+      <c r="F19" s="110"/>
+      <c r="G19" s="110"/>
+      <c r="H19" s="110"/>
+      <c r="I19" s="110"/>
+      <c r="J19" s="110"/>
+      <c r="K19" s="110"/>
+      <c r="L19" s="110"/>
       <c r="M19" s="32" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="10">
         <v>1</v>
       </c>
       <c r="B20" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="C20" s="118"/>
-      <c r="D20" s="118"/>
-      <c r="E20" s="118"/>
-      <c r="F20" s="118"/>
-      <c r="G20" s="118"/>
-      <c r="H20" s="118"/>
-      <c r="I20" s="118"/>
-      <c r="J20" s="118"/>
-      <c r="K20" s="118"/>
-      <c r="L20" s="118"/>
+      <c r="C20" s="110"/>
+      <c r="D20" s="110"/>
+      <c r="E20" s="110"/>
+      <c r="F20" s="110"/>
+      <c r="G20" s="110"/>
+      <c r="H20" s="110"/>
+      <c r="I20" s="110"/>
+      <c r="J20" s="110"/>
+      <c r="K20" s="110"/>
+      <c r="L20" s="110"/>
       <c r="M20" s="34" t="e">
         <f>+#REF!+H20+K20</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="21" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="10">
         <v>2</v>
       </c>
       <c r="B21" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="C21" s="118"/>
-      <c r="D21" s="118"/>
-      <c r="E21" s="118"/>
-      <c r="F21" s="118"/>
-      <c r="G21" s="118"/>
-      <c r="H21" s="118"/>
-      <c r="I21" s="118"/>
-      <c r="J21" s="118"/>
-      <c r="K21" s="118"/>
-      <c r="L21" s="118"/>
+      <c r="C21" s="110"/>
+      <c r="D21" s="110"/>
+      <c r="E21" s="110"/>
+      <c r="F21" s="110"/>
+      <c r="G21" s="110"/>
+      <c r="H21" s="110"/>
+      <c r="I21" s="110"/>
+      <c r="J21" s="110"/>
+      <c r="K21" s="110"/>
+      <c r="L21" s="110"/>
       <c r="M21" s="34" t="e">
         <f>+#REF!+H21+K21</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="22" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="10">
         <v>3</v>
       </c>
       <c r="B22" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="C22" s="118"/>
-      <c r="D22" s="118"/>
-      <c r="E22" s="118"/>
-      <c r="F22" s="118"/>
-      <c r="G22" s="118"/>
-      <c r="H22" s="118"/>
-      <c r="I22" s="118"/>
-      <c r="J22" s="118"/>
-      <c r="K22" s="118"/>
-      <c r="L22" s="118"/>
+      <c r="C22" s="110"/>
+      <c r="D22" s="110"/>
+      <c r="E22" s="110"/>
+      <c r="F22" s="110"/>
+      <c r="G22" s="110"/>
+      <c r="H22" s="110"/>
+      <c r="I22" s="110"/>
+      <c r="J22" s="110"/>
+      <c r="K22" s="110"/>
+      <c r="L22" s="110"/>
       <c r="M22" s="34" t="e">
         <f>+#REF!+H22+K22</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="23" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="10">
         <v>4</v>
       </c>
       <c r="B23" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="C23" s="118"/>
-      <c r="D23" s="118"/>
-      <c r="E23" s="118"/>
-      <c r="F23" s="118"/>
-      <c r="G23" s="118"/>
-      <c r="H23" s="118"/>
-      <c r="I23" s="118"/>
-      <c r="J23" s="118"/>
-      <c r="K23" s="118"/>
-      <c r="L23" s="118"/>
+      <c r="C23" s="110"/>
+      <c r="D23" s="110"/>
+      <c r="E23" s="110"/>
+      <c r="F23" s="110"/>
+      <c r="G23" s="110"/>
+      <c r="H23" s="110"/>
+      <c r="I23" s="110"/>
+      <c r="J23" s="110"/>
+      <c r="K23" s="110"/>
+      <c r="L23" s="110"/>
       <c r="M23" s="34" t="e">
         <f>+#REF!+H23+K23</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="24" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="10">
         <v>5</v>
       </c>
       <c r="B24" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="C24" s="118"/>
-      <c r="D24" s="118"/>
-      <c r="E24" s="118"/>
-      <c r="F24" s="118"/>
-      <c r="G24" s="118"/>
-      <c r="H24" s="118"/>
-      <c r="I24" s="118"/>
-      <c r="J24" s="118"/>
-      <c r="K24" s="118"/>
-      <c r="L24" s="118"/>
+      <c r="C24" s="110"/>
+      <c r="D24" s="110"/>
+      <c r="E24" s="110"/>
+      <c r="F24" s="110"/>
+      <c r="G24" s="110"/>
+      <c r="H24" s="110"/>
+      <c r="I24" s="110"/>
+      <c r="J24" s="110"/>
+      <c r="K24" s="110"/>
+      <c r="L24" s="110"/>
       <c r="M24" s="34" t="e">
         <f>+#REF!+H24+K24</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="25" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="10">
         <v>6</v>
       </c>
       <c r="B25" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="C25" s="118"/>
-      <c r="D25" s="118"/>
-      <c r="E25" s="118"/>
-      <c r="F25" s="118"/>
-      <c r="G25" s="118"/>
-      <c r="H25" s="118"/>
-      <c r="I25" s="118"/>
-      <c r="J25" s="118"/>
-      <c r="K25" s="118"/>
-      <c r="L25" s="118"/>
+      <c r="C25" s="110"/>
+      <c r="D25" s="110"/>
+      <c r="E25" s="110"/>
+      <c r="F25" s="110"/>
+      <c r="G25" s="110"/>
+      <c r="H25" s="110"/>
+      <c r="I25" s="110"/>
+      <c r="J25" s="110"/>
+      <c r="K25" s="110"/>
+      <c r="L25" s="110"/>
       <c r="M25" s="34" t="e">
         <f>+#REF!+H25+K25</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="26" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="10">
         <v>7</v>
       </c>
       <c r="B26" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="C26" s="118"/>
-      <c r="D26" s="118"/>
-      <c r="E26" s="118"/>
-      <c r="F26" s="118"/>
-      <c r="G26" s="118"/>
-      <c r="H26" s="118"/>
-      <c r="I26" s="118"/>
-      <c r="J26" s="118"/>
-      <c r="K26" s="118"/>
-      <c r="L26" s="118"/>
+      <c r="C26" s="110"/>
+      <c r="D26" s="110"/>
+      <c r="E26" s="110"/>
+      <c r="F26" s="110"/>
+      <c r="G26" s="110"/>
+      <c r="H26" s="110"/>
+      <c r="I26" s="110"/>
+      <c r="J26" s="110"/>
+      <c r="K26" s="110"/>
+      <c r="L26" s="110"/>
       <c r="M26" s="34" t="e">
         <f>+#REF!+H26+K26</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="27" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="10">
         <v>8</v>
       </c>
       <c r="B27" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="C27" s="118"/>
-      <c r="D27" s="118"/>
-      <c r="E27" s="118"/>
-      <c r="F27" s="118"/>
-      <c r="G27" s="118"/>
-      <c r="H27" s="118"/>
-      <c r="I27" s="118"/>
-      <c r="J27" s="118"/>
-      <c r="K27" s="118"/>
-      <c r="L27" s="118"/>
+      <c r="C27" s="110"/>
+      <c r="D27" s="110"/>
+      <c r="E27" s="110"/>
+      <c r="F27" s="110"/>
+      <c r="G27" s="110"/>
+      <c r="H27" s="110"/>
+      <c r="I27" s="110"/>
+      <c r="J27" s="110"/>
+      <c r="K27" s="110"/>
+      <c r="L27" s="110"/>
       <c r="M27" s="34" t="e">
         <f>+#REF!+H27+K27</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="28" spans="1:13" ht="15.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:13" ht="15.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="8" t="s">
         <v>10</v>
       </c>
       <c r="B28" s="9"/>
-      <c r="C28" s="118"/>
-      <c r="D28" s="118"/>
-      <c r="E28" s="118"/>
-      <c r="F28" s="118"/>
-      <c r="G28" s="118"/>
-      <c r="H28" s="118"/>
-      <c r="I28" s="118"/>
-      <c r="J28" s="118"/>
-      <c r="K28" s="118"/>
-      <c r="L28" s="118"/>
+      <c r="C28" s="110"/>
+      <c r="D28" s="110"/>
+      <c r="E28" s="110"/>
+      <c r="F28" s="110"/>
+      <c r="G28" s="110"/>
+      <c r="H28" s="110"/>
+      <c r="I28" s="110"/>
+      <c r="J28" s="110"/>
+      <c r="K28" s="110"/>
+      <c r="L28" s="110"/>
       <c r="M28" s="35" t="e">
         <f>SUM(M20:M27)</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="C29" s="118"/>
-      <c r="D29" s="118"/>
-      <c r="E29" s="118"/>
-      <c r="F29" s="118"/>
-      <c r="G29" s="118"/>
-      <c r="H29" s="118"/>
-      <c r="I29" s="118"/>
-      <c r="J29" s="118"/>
-      <c r="K29" s="118"/>
-      <c r="L29" s="118"/>
-    </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="C30" s="118"/>
-      <c r="D30" s="118"/>
-      <c r="E30" s="118"/>
-      <c r="F30" s="118"/>
-      <c r="G30" s="118"/>
-      <c r="H30" s="118"/>
-      <c r="I30" s="118"/>
-      <c r="J30" s="118"/>
-      <c r="K30" s="118"/>
-      <c r="L30" s="118"/>
-    </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="C31" s="118"/>
-      <c r="D31" s="118"/>
-      <c r="E31" s="118"/>
-      <c r="F31" s="118"/>
-      <c r="G31" s="118"/>
-      <c r="H31" s="118"/>
-      <c r="I31" s="118"/>
-      <c r="J31" s="118"/>
-      <c r="K31" s="118"/>
-      <c r="L31" s="118"/>
-    </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="C32" s="118"/>
-      <c r="D32" s="118"/>
-      <c r="E32" s="118"/>
-      <c r="F32" s="118"/>
-      <c r="G32" s="118"/>
-      <c r="H32" s="118"/>
-      <c r="I32" s="118"/>
-      <c r="J32" s="118"/>
-      <c r="K32" s="118"/>
-      <c r="L32" s="118"/>
-    </row>
-    <row r="39" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="C29" s="110"/>
+      <c r="D29" s="110"/>
+      <c r="E29" s="110"/>
+      <c r="F29" s="110"/>
+      <c r="G29" s="110"/>
+      <c r="H29" s="110"/>
+      <c r="I29" s="110"/>
+      <c r="J29" s="110"/>
+      <c r="K29" s="110"/>
+      <c r="L29" s="110"/>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="C30" s="110"/>
+      <c r="D30" s="110"/>
+      <c r="E30" s="110"/>
+      <c r="F30" s="110"/>
+      <c r="G30" s="110"/>
+      <c r="H30" s="110"/>
+      <c r="I30" s="110"/>
+      <c r="J30" s="110"/>
+      <c r="K30" s="110"/>
+      <c r="L30" s="110"/>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="C31" s="110"/>
+      <c r="D31" s="110"/>
+      <c r="E31" s="110"/>
+      <c r="F31" s="110"/>
+      <c r="G31" s="110"/>
+      <c r="H31" s="110"/>
+      <c r="I31" s="110"/>
+      <c r="J31" s="110"/>
+      <c r="K31" s="110"/>
+      <c r="L31" s="110"/>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="C32" s="110"/>
+      <c r="D32" s="110"/>
+      <c r="E32" s="110"/>
+      <c r="F32" s="110"/>
+      <c r="G32" s="110"/>
+      <c r="H32" s="110"/>
+      <c r="I32" s="110"/>
+      <c r="J32" s="110"/>
+      <c r="K32" s="110"/>
+      <c r="L32" s="110"/>
+    </row>
+    <row r="39" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E39" s="39"/>
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="C15:L32"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="K3:K4"/>
-    <mergeCell ref="L3:L4"/>
     <mergeCell ref="M3:M4"/>
     <mergeCell ref="H3:H4"/>
     <mergeCell ref="F3:F4"/>
@@ -2755,6 +2762,11 @@
     <mergeCell ref="J3:J4"/>
     <mergeCell ref="I3:I4"/>
     <mergeCell ref="E3:E4"/>
+    <mergeCell ref="C15:L32"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="K3:K4"/>
+    <mergeCell ref="L3:L4"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -2765,29 +2777,29 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:L13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.33203125" customWidth="1"/>
-    <col min="3" max="3" width="14.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.33203125" customWidth="1"/>
-    <col min="5" max="5" width="13.109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.109375" customWidth="1"/>
+    <col min="1" max="1" width="6.28515625" customWidth="1"/>
+    <col min="3" max="3" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.28515625" customWidth="1"/>
+    <col min="5" max="5" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.140625" customWidth="1"/>
     <col min="7" max="7" width="18" customWidth="1"/>
-    <col min="8" max="8" width="11.109375" customWidth="1"/>
-    <col min="9" max="9" width="14.6640625" customWidth="1"/>
+    <col min="8" max="8" width="11.140625" customWidth="1"/>
+    <col min="9" max="9" width="14.7109375" customWidth="1"/>
     <col min="10" max="10" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="91" t="s">
         <v>48</v>
       </c>
       <c r="B1" s="92"/>
       <c r="C1" s="93"/>
-      <c r="D1" s="121">
-        <v>0</v>
-      </c>
-      <c r="E1" s="121"/>
+      <c r="D1" s="122">
+        <v>0</v>
+      </c>
+      <c r="E1" s="122"/>
       <c r="F1" s="103"/>
       <c r="G1" s="93"/>
       <c r="H1" s="93"/>
@@ -2795,9 +2807,9 @@
       <c r="J1" s="94"/>
       <c r="L1" s="17"/>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="95" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B2" s="88"/>
       <c r="C2" s="89"/>
@@ -2812,53 +2824,53 @@
       <c r="J2" s="96"/>
       <c r="L2" s="17"/>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A3" s="122" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="116" t="s">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" s="123" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="111" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="116" t="s">
+      <c r="C3" s="111" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="114" t="s">
+      <c r="D3" s="120" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="113" t="s">
+      <c r="E3" s="119" t="s">
         <v>51</v>
       </c>
-      <c r="F3" s="116" t="s">
-        <v>79</v>
-      </c>
-      <c r="G3" s="114" t="s">
+      <c r="F3" s="111" t="s">
+        <v>78</v>
+      </c>
+      <c r="G3" s="120" t="s">
         <v>44</v>
       </c>
-      <c r="H3" s="113" t="s">
+      <c r="H3" s="119" t="s">
         <v>6</v>
       </c>
-      <c r="I3" s="125" t="s">
-        <v>75</v>
-      </c>
-      <c r="J3" s="124" t="s">
-        <v>53</v>
+      <c r="I3" s="126" t="s">
+        <v>74</v>
+      </c>
+      <c r="J3" s="125" t="s">
+        <v>52</v>
       </c>
       <c r="L3" s="17"/>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A4" s="123"/>
-      <c r="B4" s="117"/>
-      <c r="C4" s="117"/>
-      <c r="D4" s="114"/>
-      <c r="E4" s="113"/>
-      <c r="F4" s="117"/>
-      <c r="G4" s="114"/>
-      <c r="H4" s="113"/>
-      <c r="I4" s="125"/>
-      <c r="J4" s="124"/>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A4" s="124"/>
+      <c r="B4" s="112"/>
+      <c r="C4" s="112"/>
+      <c r="D4" s="120"/>
+      <c r="E4" s="119"/>
+      <c r="F4" s="112"/>
+      <c r="G4" s="120"/>
+      <c r="H4" s="119"/>
+      <c r="I4" s="126"/>
+      <c r="J4" s="125"/>
       <c r="L4" s="17"/>
     </row>
-    <row r="5" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="98">
         <v>1</v>
       </c>
@@ -2895,7 +2907,7 @@
       </c>
       <c r="L5" s="17"/>
     </row>
-    <row r="6" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="98">
         <v>2</v>
       </c>
@@ -2932,7 +2944,7 @@
       </c>
       <c r="L6" s="17"/>
     </row>
-    <row r="7" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="98">
         <v>3</v>
       </c>
@@ -2970,7 +2982,7 @@
       </c>
       <c r="L7" s="17"/>
     </row>
-    <row r="8" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="98">
         <v>4</v>
       </c>
@@ -3007,7 +3019,7 @@
       </c>
       <c r="L8" s="17"/>
     </row>
-    <row r="9" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="98">
         <v>5</v>
       </c>
@@ -3044,7 +3056,7 @@
       </c>
       <c r="L9" s="17"/>
     </row>
-    <row r="10" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="98">
         <v>6</v>
       </c>
@@ -3081,7 +3093,7 @@
       </c>
       <c r="L10" s="17"/>
     </row>
-    <row r="11" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="98">
         <v>7</v>
       </c>
@@ -3119,7 +3131,7 @@
       </c>
       <c r="L11" s="17"/>
     </row>
-    <row r="12" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="98">
         <v>8</v>
       </c>
@@ -3157,7 +3169,7 @@
       </c>
       <c r="L12" s="17"/>
     </row>
-    <row r="13" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="77" t="s">
         <v>10</v>
       </c>
